--- a/Convert_from_xlsx_to_Json/table_normalization/education-table05.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/education-table05.xlsx
@@ -457,7 +457,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,12 +473,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,7 +529,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -565,7 +559,6 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="29">
     <cellStyle name="Comma 4 3 2" xfId="2"/>
@@ -2370,7 +2363,7 @@
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="A10" s="4"/>
-      <c r="B10" s="15"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="6">
         <v>201415</v>
       </c>
